--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.36574989737657</v>
+      </c>
+      <c r="C2">
         <v>22.75814456842184</v>
-      </c>
-      <c r="C2">
-        <v>27.36574989737657</v>
       </c>
       <c r="D2">
         <v>4.394031319176847</v>
       </c>
       <c r="E2">
-        <v>15.1595751291988</v>
+        <v>18.22877696768725</v>
       </c>
       <c r="F2">
         <v>66.61164790311395</v>
       </c>
       <c r="G2">
-        <v>18.22877696768725</v>
+        <v>15.1595751291988</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.25381070542361</v>
+      </c>
+      <c r="C3">
         <v>21.35767458348104</v>
-      </c>
-      <c r="C3">
-        <v>29.25381070542361</v>
       </c>
       <c r="D3">
         <v>4.682157676348548</v>
       </c>
       <c r="E3">
-        <v>14.18064136510738</v>
+        <v>19.42335981170933</v>
       </c>
       <c r="F3">
         <v>66.39599882318329</v>
       </c>
       <c r="G3">
-        <v>19.42335981170933</v>
+        <v>14.18064136510738</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>36.9542066027689</v>
+      </c>
+      <c r="C4">
         <v>15.33546325878594</v>
-      </c>
-      <c r="C4">
-        <v>36.9542066027689</v>
       </c>
       <c r="D4">
         <v>6.520833333333333</v>
       </c>
       <c r="E4">
-        <v>10.06993006993007</v>
+        <v>24.26573426573426</v>
       </c>
       <c r="F4">
         <v>65.66433566433567</v>
       </c>
       <c r="G4">
-        <v>24.26573426573426</v>
+        <v>10.06993006993007</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.1014213442544</v>
+      </c>
+      <c r="C5">
         <v>31.65502288605155</v>
-      </c>
-      <c r="C5">
-        <v>29.1014213442544</v>
       </c>
       <c r="D5">
         <v>3.159056316590563</v>
       </c>
       <c r="E5">
-        <v>19.69129327139218</v>
+        <v>18.10280233777911</v>
       </c>
       <c r="F5">
         <v>62.20590439082872</v>
       </c>
       <c r="G5">
-        <v>18.10280233777911</v>
+        <v>19.69129327139218</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.34142404344938</v>
+      </c>
+      <c r="C6">
         <v>20.63425338187199</v>
-      </c>
-      <c r="C6">
-        <v>30.34142404344938</v>
       </c>
       <c r="D6">
         <v>4.846310556981624</v>
       </c>
       <c r="E6">
-        <v>13.66726994292079</v>
+        <v>20.09689544758457</v>
       </c>
       <c r="F6">
         <v>66.23583460949463</v>
       </c>
       <c r="G6">
-        <v>20.09689544758457</v>
+        <v>13.66726994292079</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.34645669291339</v>
+      </c>
+      <c r="C7">
         <v>23.62204724409449</v>
-      </c>
-      <c r="C7">
-        <v>28.34645669291339</v>
       </c>
       <c r="D7">
         <v>4.233333333333333</v>
       </c>
       <c r="E7">
-        <v>15.5440414507772</v>
+        <v>18.65284974093264</v>
       </c>
       <c r="F7">
         <v>65.80310880829015</v>
       </c>
       <c r="G7">
-        <v>18.65284974093264</v>
+        <v>15.5440414507772</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.5693135935397</v>
+      </c>
+      <c r="C8">
         <v>17.56393001345895</v>
-      </c>
-      <c r="C8">
-        <v>29.5693135935397</v>
       </c>
       <c r="D8">
         <v>5.693486590038314</v>
       </c>
       <c r="E8">
-        <v>11.93743139407245</v>
+        <v>20.09696304427369</v>
       </c>
       <c r="F8">
         <v>67.96560556165386</v>
       </c>
       <c r="G8">
-        <v>20.09696304427369</v>
+        <v>11.93743139407245</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.40209832865683</v>
+      </c>
+      <c r="C9">
         <v>32.066609735269</v>
-      </c>
-      <c r="C9">
-        <v>32.40209832865683</v>
       </c>
       <c r="D9">
         <v>3.118508655126498</v>
       </c>
       <c r="E9">
-        <v>19.49708860290027</v>
+        <v>19.70107183918703</v>
       </c>
       <c r="F9">
         <v>60.8018395579127</v>
       </c>
       <c r="G9">
-        <v>19.70107183918703</v>
+        <v>19.49708860290027</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.81566677028287</v>
+      </c>
+      <c r="C10">
         <v>24.12185265775567</v>
-      </c>
-      <c r="C10">
-        <v>28.81566677028287</v>
       </c>
       <c r="D10">
         <v>4.145618556701031</v>
       </c>
       <c r="E10">
-        <v>15.77235772357724</v>
+        <v>18.84146341463414</v>
       </c>
       <c r="F10">
         <v>65.38617886178862</v>
       </c>
       <c r="G10">
-        <v>18.84146341463414</v>
+        <v>15.77235772357724</v>
       </c>
     </row>
   </sheetData>
